--- a/public/prices.xlsx
+++ b/public/prices.xlsx
@@ -83,30 +83,20 @@
           <t xml:space="preserve">Сосиски «Из говядины» (80 г × 6 шт)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.48</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">290</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">263.64</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48.33</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.1</t>
-        </is>
+      <c r="C2" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="D2" t="n">
+        <v>290</v>
+      </c>
+      <c r="E2" t="n">
+        <v>263.64</v>
+      </c>
+      <c r="F2" t="n">
+        <v>48.33</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.1</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -140,30 +130,20 @@
           <t xml:space="preserve">Сосиски «Два мяса» (80 г × 6 шт)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.48</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">286</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">47.67</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.05</t>
-        </is>
+      <c r="C3" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="D3" t="n">
+        <v>286</v>
+      </c>
+      <c r="E3" t="n">
+        <v>260</v>
+      </c>
+      <c r="F3" t="n">
+        <v>47.67</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.05</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -197,30 +177,20 @@
           <t xml:space="preserve">Сосиски «Три перца с сыром» (80 г × 6 шт)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.48</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">316</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">287.27</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52.67</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.37</t>
-        </is>
+      <c r="C4" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="D4" t="n">
+        <v>316</v>
+      </c>
+      <c r="E4" t="n">
+        <v>287.27</v>
+      </c>
+      <c r="F4" t="n">
+        <v>52.67</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.37</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -254,30 +224,20 @@
           <t xml:space="preserve">Сосиски «Куриные» (80 г × 6 шт)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.48</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">286</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">47.67</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.05</t>
-        </is>
+      <c r="C5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="D5" t="n">
+        <v>286</v>
+      </c>
+      <c r="E5" t="n">
+        <v>260</v>
+      </c>
+      <c r="F5" t="n">
+        <v>47.67</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3.05</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -311,30 +271,20 @@
           <t xml:space="preserve">Сосиски «С бараниной» (80 г × 6 шт)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.48</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">366</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">332.73</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">61</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.91</t>
-        </is>
+      <c r="C6" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="D6" t="n">
+        <v>366</v>
+      </c>
+      <c r="E6" t="n">
+        <v>332.73</v>
+      </c>
+      <c r="F6" t="n">
+        <v>61</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.91</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -368,30 +318,20 @@
           <t xml:space="preserve">Сосиски «С травами» (130 г × 5 шт)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.65</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">424</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">385.45</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84.8</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.53</t>
-        </is>
+      <c r="C7" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="D7" t="n">
+        <v>424</v>
+      </c>
+      <c r="E7" t="n">
+        <v>385.45</v>
+      </c>
+      <c r="F7" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.53</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -425,30 +365,20 @@
           <t xml:space="preserve">Сосиски «С сыром» (130 г × 5 шт)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.65</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">455</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">413.64</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">91</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.86</t>
-        </is>
+      <c r="C8" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="D8" t="n">
+        <v>455</v>
+      </c>
+      <c r="E8" t="n">
+        <v>413.64</v>
+      </c>
+      <c r="F8" t="n">
+        <v>91</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4.86</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -482,30 +412,20 @@
           <t xml:space="preserve">Сосиски Из конины" (80 г х 6 шт)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.48</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">316</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">287.27</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52.67</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.37</t>
-        </is>
+      <c r="C9" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="D9" t="n">
+        <v>316</v>
+      </c>
+      <c r="E9" t="n">
+        <v>287.27</v>
+      </c>
+      <c r="F9" t="n">
+        <v>52.67</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.37</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -539,30 +459,20 @@
           <t xml:space="preserve">Котлета говяжья прожаренная (100 г × 3 шт)</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.3</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">276</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250.91</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.95</t>
-        </is>
+      <c r="C10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>276</v>
+      </c>
+      <c r="E10" t="n">
+        <v>250.91</v>
+      </c>
+      <c r="F10" t="n">
+        <v>92</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.95</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -596,30 +506,20 @@
           <t xml:space="preserve">Котлета говяжья прожаренная (150 г × 2 шт)</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.3</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">276</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250.91</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">138</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.95</t>
-        </is>
+      <c r="C11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>276</v>
+      </c>
+      <c r="E11" t="n">
+        <v>250.91</v>
+      </c>
+      <c r="F11" t="n">
+        <v>138</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.95</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -653,30 +553,22 @@
           <t xml:space="preserve">Ветчина Куриная Филейная в нарезке</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.5</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170.91</t>
-        </is>
+      <c r="C12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>188</v>
+      </c>
+      <c r="E12" t="n">
+        <v>170.91</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.01</t>
-        </is>
+      <c r="G12" t="n">
+        <v>2.01</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -710,30 +602,22 @@
           <t xml:space="preserve">Пепперони варено-копченый куриный нарезка</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.5</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">274</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249.09</t>
-        </is>
+      <c r="C13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>274</v>
+      </c>
+      <c r="E13" t="n">
+        <v>249.09</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.92</t>
-        </is>
+      <c r="G13" t="n">
+        <v>2.92</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -767,30 +651,22 @@
           <t xml:space="preserve">Пепперони варено-копченый куриный целый батон</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.8</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">457</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">415.45</t>
-        </is>
+      <c r="C14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D14" t="n">
+        <v>457</v>
+      </c>
+      <c r="E14" t="n">
+        <v>415.45</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.88</t>
-        </is>
+      <c r="G14" t="n">
+        <v>4.88</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -829,25 +705,19 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">412</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">374.55</t>
-        </is>
+      <c r="D15" t="n">
+        <v>412</v>
+      </c>
+      <c r="E15" t="n">
+        <v>374.55</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.4</t>
-        </is>
+      <c r="G15" t="n">
+        <v>4.4</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -945,30 +815,22 @@
           <t xml:space="preserve">Сосиски «К завтраку» (без оболочки) для «Сосиски в тесте» 45 гр - вес сосиски</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">245</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222.73</t>
-        </is>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>245</v>
+      </c>
+      <c r="E2" t="n">
+        <v>222.73</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.62</t>
-        </is>
+      <c r="G2" t="n">
+        <v>2.62</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1002,30 +864,22 @@
           <t xml:space="preserve">Сосиски «К завтраку»</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.4</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">135</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122.73</t>
-        </is>
+      <c r="C3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>135</v>
+      </c>
+      <c r="E3" t="n">
+        <v>122.73</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.44</t>
-        </is>
+      <c r="G3" t="n">
+        <v>1.44</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1059,30 +913,22 @@
           <t xml:space="preserve">Сосиски «Нежные»</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.4</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164.55</t>
-        </is>
+      <c r="C4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>181</v>
+      </c>
+      <c r="E4" t="n">
+        <v>164.55</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.93</t>
-        </is>
+      <c r="G4" t="n">
+        <v>1.93</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1116,30 +962,22 @@
           <t xml:space="preserve">Сосиски «Казанские с молоком»</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.4</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">235</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213.64</t>
-        </is>
+      <c r="C5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>235</v>
+      </c>
+      <c r="E5" t="n">
+        <v>213.64</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.51</t>
-        </is>
+      <c r="G5" t="n">
+        <v>2.51</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1173,30 +1011,22 @@
           <t xml:space="preserve">Сосиски «С сыром»</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.4</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">293</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">266.36</t>
-        </is>
+      <c r="C6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>293</v>
+      </c>
+      <c r="E6" t="n">
+        <v>266.36</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.13</t>
-        </is>
+      <c r="G6" t="n">
+        <v>3.13</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1230,30 +1060,22 @@
           <t xml:space="preserve">Сосиски "Из говядины"</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.4</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">284</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258.18</t>
-        </is>
+      <c r="C7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>284</v>
+      </c>
+      <c r="E7" t="n">
+        <v>258.18</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.03</t>
-        </is>
+      <c r="G7" t="n">
+        <v>3.03</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1287,30 +1109,22 @@
           <t xml:space="preserve">Сосиски в/с Премиум</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.4</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132.73</t>
-        </is>
+      <c r="C8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>146</v>
+      </c>
+      <c r="E8" t="n">
+        <v>132.73</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.56</t>
-        </is>
+      <c r="G8" t="n">
+        <v>1.56</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1344,30 +1158,22 @@
           <t xml:space="preserve">Сосиски в/с Сочные</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.4</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130.91</t>
-        </is>
+      <c r="C9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>144</v>
+      </c>
+      <c r="E9" t="n">
+        <v>130.91</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.54</t>
-        </is>
+      <c r="G9" t="n">
+        <v>1.54</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1401,30 +1207,22 @@
           <t xml:space="preserve">Колбаски с Сыром</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.3</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">271</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246.36</t>
-        </is>
+      <c r="C10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>271</v>
+      </c>
+      <c r="E10" t="n">
+        <v>246.36</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.89</t>
-        </is>
+      <c r="G10" t="n">
+        <v>2.89</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1458,30 +1256,22 @@
           <t xml:space="preserve">Вареная «Из Говядины»</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.5</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">265.45</t>
-        </is>
+      <c r="C11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>292</v>
+      </c>
+      <c r="E11" t="n">
+        <v>265.45</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.12</t>
-        </is>
+      <c r="G11" t="n">
+        <v>3.12</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1515,30 +1305,22 @@
           <t xml:space="preserve">Вареная Ассорти</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.5</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179.09</t>
-        </is>
+      <c r="C12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>197</v>
+      </c>
+      <c r="E12" t="n">
+        <v>179.09</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.1</t>
-        </is>
+      <c r="G12" t="n">
+        <v>2.1</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1572,30 +1354,22 @@
           <t xml:space="preserve">Вареная Нежная</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.5</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181.82</t>
-        </is>
+      <c r="C13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>200</v>
+      </c>
+      <c r="E13" t="n">
+        <v>181.82</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.14</t>
-        </is>
+      <c r="G13" t="n">
+        <v>2.14</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1629,30 +1403,22 @@
           <t xml:space="preserve">Ветчина из Индейки</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.5</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">380</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">345.45</t>
-        </is>
+      <c r="C14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>380</v>
+      </c>
+      <c r="E14" t="n">
+        <v>345.45</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.06</t>
-        </is>
+      <c r="G14" t="n">
+        <v>4.06</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1686,30 +1452,22 @@
           <t xml:space="preserve">Ветчина Мраморная с говядиной</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.5</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">398</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">361.82</t>
-        </is>
+      <c r="C15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>398</v>
+      </c>
+      <c r="E15" t="n">
+        <v>361.82</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.25</t>
-        </is>
+      <c r="G15" t="n">
+        <v>4.25</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1743,30 +1501,22 @@
           <t xml:space="preserve">Ветчина из Курицы</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.5</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">350</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">318.18</t>
-        </is>
+      <c r="C16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>350</v>
+      </c>
+      <c r="E16" t="n">
+        <v>318.18</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.74</t>
-        </is>
+      <c r="G16" t="n">
+        <v>3.74</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1800,30 +1550,22 @@
           <t xml:space="preserve">Сервелат Ханский</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.45</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196.36</t>
-        </is>
+      <c r="C17" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D17" t="n">
+        <v>216</v>
+      </c>
+      <c r="E17" t="n">
+        <v>196.36</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.31</t>
-        </is>
+      <c r="G17" t="n">
+        <v>2.31</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1857,30 +1599,22 @@
           <t xml:space="preserve">Сервелат по-татарски в/к</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.45</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">298</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">270.91</t>
-        </is>
+      <c r="C18" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D18" t="n">
+        <v>298</v>
+      </c>
+      <c r="E18" t="n">
+        <v>270.91</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.18</t>
-        </is>
+      <c r="G18" t="n">
+        <v>3.18</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1914,30 +1648,22 @@
           <t xml:space="preserve">Полукопченая из Индейки</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.45</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">348</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">316.36</t>
-        </is>
+      <c r="C19" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D19" t="n">
+        <v>348</v>
+      </c>
+      <c r="E19" t="n">
+        <v>316.36</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.71</t>
-        </is>
+      <c r="G19" t="n">
+        <v>3.71</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1971,30 +1697,22 @@
           <t xml:space="preserve">Полукопченая из Говядины</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.45</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">358</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">325.45</t>
-        </is>
+      <c r="C20" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D20" t="n">
+        <v>358</v>
+      </c>
+      <c r="E20" t="n">
+        <v>325.45</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.82</t>
-        </is>
+      <c r="G20" t="n">
+        <v>3.82</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2028,30 +1746,22 @@
           <t xml:space="preserve">в/к Рамазан</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.54</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">377</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">342.73</t>
-        </is>
+      <c r="C21" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="D21" t="n">
+        <v>377</v>
+      </c>
+      <c r="E21" t="n">
+        <v>342.73</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.02</t>
-        </is>
+      <c r="G21" t="n">
+        <v>4.02</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2085,30 +1795,22 @@
           <t xml:space="preserve">в/к Рамазан (половинка)</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.27</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170.91</t>
-        </is>
+      <c r="C22" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="D22" t="n">
+        <v>188</v>
+      </c>
+      <c r="E22" t="n">
+        <v>170.91</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.01</t>
-        </is>
+      <c r="G22" t="n">
+        <v>2.01</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -2142,30 +1844,22 @@
           <t xml:space="preserve">в/к Мраморная</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.54</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">362</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">329.09</t>
-        </is>
+      <c r="C23" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="D23" t="n">
+        <v>362</v>
+      </c>
+      <c r="E23" t="n">
+        <v>329.09</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.86</t>
-        </is>
+      <c r="G23" t="n">
+        <v>3.86</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -2199,30 +1893,22 @@
           <t xml:space="preserve">в/к Мраморная (половинка)</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.27</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164.55</t>
-        </is>
+      <c r="C24" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="D24" t="n">
+        <v>181</v>
+      </c>
+      <c r="E24" t="n">
+        <v>164.55</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.93</t>
-        </is>
+      <c r="G24" t="n">
+        <v>1.93</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -2256,30 +1942,22 @@
           <t xml:space="preserve">в/к Филейный</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.54</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">333</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">302.73</t>
-        </is>
+      <c r="C25" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="D25" t="n">
+        <v>333</v>
+      </c>
+      <c r="E25" t="n">
+        <v>302.73</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.55</t>
-        </is>
+      <c r="G25" t="n">
+        <v>3.55</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -2313,30 +1991,22 @@
           <t xml:space="preserve">в/к Филейный (половинка)</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.27</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150.91</t>
-        </is>
+      <c r="C26" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="D26" t="n">
+        <v>166</v>
+      </c>
+      <c r="E26" t="n">
+        <v>150.91</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.77</t>
-        </is>
+      <c r="G26" t="n">
+        <v>1.77</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2370,30 +2040,22 @@
           <t xml:space="preserve">в/к Княжеская</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.54</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">362</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">329.09</t>
-        </is>
+      <c r="C27" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="D27" t="n">
+        <v>362</v>
+      </c>
+      <c r="E27" t="n">
+        <v>329.09</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.86</t>
-        </is>
+      <c r="G27" t="n">
+        <v>3.86</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -2427,30 +2089,22 @@
           <t xml:space="preserve">в/к Княжеская (половинка)</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.27</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164.55</t>
-        </is>
+      <c r="C28" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="D28" t="n">
+        <v>181</v>
+      </c>
+      <c r="E28" t="n">
+        <v>164.55</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.93</t>
-        </is>
+      <c r="G28" t="n">
+        <v>1.93</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -2484,30 +2138,22 @@
           <t xml:space="preserve">Казылык «Премиум» в подарочной упаковке</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.2</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">650</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">541.67</t>
-        </is>
+      <c r="C29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D29" t="n">
+        <v>650</v>
+      </c>
+      <c r="E29" t="n">
+        <v>541.67</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6.36</t>
-        </is>
+      <c r="G29" t="n">
+        <v>6.36</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2541,30 +2187,22 @@
           <t xml:space="preserve">Казылык «Премиум» в нарезке в подарочной упаковке</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.1</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">450</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">375</t>
-        </is>
+      <c r="C30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>450</v>
+      </c>
+      <c r="E30" t="n">
+        <v>375</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.4</t>
-        </is>
+      <c r="G30" t="n">
+        <v>4.4</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -2662,30 +2300,20 @@
           <t xml:space="preserve">Губадия с кортом</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">59.93</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">54.48</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">59.93</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.64</t>
-        </is>
+      <c r="C2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>59.93</v>
+      </c>
+      <c r="E2" t="n">
+        <v>54.48</v>
+      </c>
+      <c r="F2" t="n">
+        <v>59.93</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.64</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -2719,30 +2347,20 @@
           <t xml:space="preserve">Чебурек жареный</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">61.81</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">56.19</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">61.81</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.66</t>
-        </is>
+      <c r="C3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>61.81</v>
+      </c>
+      <c r="E3" t="n">
+        <v>56.19</v>
+      </c>
+      <c r="F3" t="n">
+        <v>61.81</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.66</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -2776,30 +2394,20 @@
           <t xml:space="preserve">Перемяч жареный</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">63.29</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57.54</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">63.29</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.68</t>
-        </is>
+      <c r="C4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>63.29</v>
+      </c>
+      <c r="E4" t="n">
+        <v>57.54</v>
+      </c>
+      <c r="F4" t="n">
+        <v>63.29</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.68</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -2833,30 +2441,20 @@
           <t xml:space="preserve">Самса с курицей</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.12</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66.05</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60.05</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66.05</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.71</t>
-        </is>
+      <c r="C5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D5" t="n">
+        <v>66.05</v>
+      </c>
+      <c r="E5" t="n">
+        <v>60.05</v>
+      </c>
+      <c r="F5" t="n">
+        <v>66.05</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.71</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -2890,30 +2488,20 @@
           <t xml:space="preserve">Эчпочмак с говядиной и картофелем</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">73.58</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66.89</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">73.58</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.79</t>
-        </is>
+      <c r="C6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>73.58</v>
+      </c>
+      <c r="E6" t="n">
+        <v>66.89</v>
+      </c>
+      <c r="F6" t="n">
+        <v>73.58</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.79</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -2947,30 +2535,20 @@
           <t xml:space="preserve">Самса с говядиной</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.12</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">78.28</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71.16</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">78.28</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.84</t>
-        </is>
+      <c r="C7" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D7" t="n">
+        <v>78.28</v>
+      </c>
+      <c r="E7" t="n">
+        <v>71.16</v>
+      </c>
+      <c r="F7" t="n">
+        <v>78.28</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.84</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -3004,30 +2582,20 @@
           <t xml:space="preserve">Элеш с курицей и картофелем</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.15</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">83.29</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">75.72</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">83.29</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.89</t>
-        </is>
+      <c r="C8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D8" t="n">
+        <v>83.29</v>
+      </c>
+      <c r="E8" t="n">
+        <v>75.72</v>
+      </c>
+      <c r="F8" t="n">
+        <v>83.29</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.89</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -3061,30 +2629,20 @@
           <t xml:space="preserve">Беккен с капустой</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52.97</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48.15</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52.97</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.57</t>
-        </is>
+      <c r="C9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>52.97</v>
+      </c>
+      <c r="E9" t="n">
+        <v>48.15</v>
+      </c>
+      <c r="F9" t="n">
+        <v>52.97</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.57</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -3118,30 +2676,20 @@
           <t xml:space="preserve">Вак балиш</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.1</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66.32</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60.29</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66.32</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.71</t>
-        </is>
+      <c r="C10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>66.32</v>
+      </c>
+      <c r="E10" t="n">
+        <v>60.29</v>
+      </c>
+      <c r="F10" t="n">
+        <v>66.32</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.71</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -3175,25 +2723,19 @@
           <t xml:space="preserve">Чак-Чак в пластиковой упаковке</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.3</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211.8</t>
-        </is>
+      <c r="C11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>211.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211.8</t>
-        </is>
+      <c r="F11" t="n">
+        <v>211.8</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -3232,25 +2774,19 @@
           <t xml:space="preserve">Чак-Чак в крафтовой подарочной упаковке</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.3</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">295.57</t>
-        </is>
+      <c r="C12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>295.57</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">295.57</t>
-        </is>
+      <c r="F12" t="n">
+        <v>295.57</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -3289,30 +2825,20 @@
           <t xml:space="preserve">Сочник с творогом</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.1</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">47.08</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42.8</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">47.08</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.5</t>
-        </is>
+      <c r="C13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>47.08</v>
+      </c>
+      <c r="E13" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="F13" t="n">
+        <v>47.08</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.5</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -3346,30 +2872,20 @@
           <t xml:space="preserve">Пирожок жареный с картофелем</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.1</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50.92</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46.29</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50.92</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.54</t>
-        </is>
+      <c r="C14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>50.92</v>
+      </c>
+      <c r="E14" t="n">
+        <v>46.29</v>
+      </c>
+      <c r="F14" t="n">
+        <v>50.92</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.54</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -3403,30 +2919,20 @@
           <t xml:space="preserve">Сырник</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.07</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48.26</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">43.87</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48.26</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.52</t>
-        </is>
+      <c r="C15" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="D15" t="n">
+        <v>48.26</v>
+      </c>
+      <c r="E15" t="n">
+        <v>43.87</v>
+      </c>
+      <c r="F15" t="n">
+        <v>48.26</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.52</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -3460,30 +2966,20 @@
           <t xml:space="preserve">Пирожок с яблоком</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.1</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52.97</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48.15</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52.97</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.57</t>
-        </is>
+      <c r="C16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>52.97</v>
+      </c>
+      <c r="E16" t="n">
+        <v>48.15</v>
+      </c>
+      <c r="F16" t="n">
+        <v>52.97</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.57</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -3517,30 +3013,20 @@
           <t xml:space="preserve">Пирожок с зеленым луком и яйцом</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.1</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">67.73</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">61.57</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">67.73</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.72</t>
-        </is>
+      <c r="C17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>67.73</v>
+      </c>
+      <c r="E17" t="n">
+        <v>61.57</v>
+      </c>
+      <c r="F17" t="n">
+        <v>67.73</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.72</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -3574,30 +3060,20 @@
           <t xml:space="preserve">Маффин апельсиновый</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.1</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72.26</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">65.69</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72.26</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.77</t>
-        </is>
+      <c r="C18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>72.26</v>
+      </c>
+      <c r="E18" t="n">
+        <v>65.69</v>
+      </c>
+      <c r="F18" t="n">
+        <v>72.26</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.77</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -3631,30 +3107,20 @@
           <t xml:space="preserve">Сосиска в тесте</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.12</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72.49</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">65.9</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72.49</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.77</t>
-        </is>
+      <c r="C19" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D19" t="n">
+        <v>72.49</v>
+      </c>
+      <c r="E19" t="n">
+        <v>65.9</v>
+      </c>
+      <c r="F19" t="n">
+        <v>72.49</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.77</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -3688,30 +3154,20 @@
           <t xml:space="preserve">Пирожок с вишней</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.1</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">75.08</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68.25</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">75.08</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.8</t>
-        </is>
+      <c r="C20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>75.08</v>
+      </c>
+      <c r="E20" t="n">
+        <v>68.25</v>
+      </c>
+      <c r="F20" t="n">
+        <v>75.08</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.8</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -3745,30 +3201,20 @@
           <t xml:space="preserve">Круассан с шоколадом и орехами</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.09</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">77.51</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70.46</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">77.51</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.83</t>
-        </is>
+      <c r="C21" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="D21" t="n">
+        <v>77.51</v>
+      </c>
+      <c r="E21" t="n">
+        <v>70.46</v>
+      </c>
+      <c r="F21" t="n">
+        <v>77.51</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.83</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -3802,30 +3248,20 @@
           <t xml:space="preserve">Маффин шоколадный</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.1</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">78.78</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71.62</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">78.78</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.84</t>
-        </is>
+      <c r="C22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>78.78</v>
+      </c>
+      <c r="E22" t="n">
+        <v>71.62</v>
+      </c>
+      <c r="F22" t="n">
+        <v>78.78</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.84</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -3859,30 +3295,20 @@
           <t xml:space="preserve">Слойка с ветчиной и сыром</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.09</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108.15</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98.32</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108.15</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.15</t>
-        </is>
+      <c r="C23" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="D23" t="n">
+        <v>108.15</v>
+      </c>
+      <c r="E23" t="n">
+        <v>98.32</v>
+      </c>
+      <c r="F23" t="n">
+        <v>108.15</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.15</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -3980,30 +3406,20 @@
           <t xml:space="preserve">Beef Sausages (80g × 6 pcs)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.48</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">290</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">263.64</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48.33</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.1</t>
-        </is>
+      <c r="C2" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="D2" t="n">
+        <v>290</v>
+      </c>
+      <c r="E2" t="n">
+        <v>263.64</v>
+      </c>
+      <c r="F2" t="n">
+        <v>48.33</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.1</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -4037,30 +3453,20 @@
           <t xml:space="preserve">Two-Meat Sausages (80g × 6 pcs)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.48</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">286</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">47.67</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.05</t>
-        </is>
+      <c r="C3" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="D3" t="n">
+        <v>286</v>
+      </c>
+      <c r="E3" t="n">
+        <v>260</v>
+      </c>
+      <c r="F3" t="n">
+        <v>47.67</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.05</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -4094,30 +3500,20 @@
           <t xml:space="preserve">Three Peppers &amp; Cheese Sausages (80g × 6 pcs)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.48</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">316</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">287.27</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52.67</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.37</t>
-        </is>
+      <c r="C4" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="D4" t="n">
+        <v>316</v>
+      </c>
+      <c r="E4" t="n">
+        <v>287.27</v>
+      </c>
+      <c r="F4" t="n">
+        <v>52.67</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.37</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -4151,30 +3547,20 @@
           <t xml:space="preserve">Chicken Sausages (80g × 6 pcs)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.48</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">286</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">47.67</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.05</t>
-        </is>
+      <c r="C5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="D5" t="n">
+        <v>286</v>
+      </c>
+      <c r="E5" t="n">
+        <v>260</v>
+      </c>
+      <c r="F5" t="n">
+        <v>47.67</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3.05</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -4208,30 +3594,20 @@
           <t xml:space="preserve">Lamb Sausages (80g × 6 pcs)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.48</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">366</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">332.73</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">61</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.91</t>
-        </is>
+      <c r="C6" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="D6" t="n">
+        <v>366</v>
+      </c>
+      <c r="E6" t="n">
+        <v>332.73</v>
+      </c>
+      <c r="F6" t="n">
+        <v>61</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.91</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -4265,30 +3641,20 @@
           <t xml:space="preserve">Herb Sausages (130g × 5 pcs)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.65</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">424</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">385.45</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84.8</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.53</t>
-        </is>
+      <c r="C7" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="D7" t="n">
+        <v>424</v>
+      </c>
+      <c r="E7" t="n">
+        <v>385.45</v>
+      </c>
+      <c r="F7" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.53</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -4322,30 +3688,20 @@
           <t xml:space="preserve">Cheese Sausages (130g × 5 pcs)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.65</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">455</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">413.64</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">91</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.86</t>
-        </is>
+      <c r="C8" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="D8" t="n">
+        <v>455</v>
+      </c>
+      <c r="E8" t="n">
+        <v>413.64</v>
+      </c>
+      <c r="F8" t="n">
+        <v>91</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4.86</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -4379,30 +3735,20 @@
           <t xml:space="preserve">Horse-Meat Sausages (80g × 6 pcs)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.48</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">316</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">287.27</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52.67</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.37</t>
-        </is>
+      <c r="C9" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="D9" t="n">
+        <v>316</v>
+      </c>
+      <c r="E9" t="n">
+        <v>287.27</v>
+      </c>
+      <c r="F9" t="n">
+        <v>52.67</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.37</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -4436,30 +3782,20 @@
           <t xml:space="preserve">Fried Beef Patty (100g × 3 pcs)</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.3</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">276</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250.91</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.95</t>
-        </is>
+      <c r="C10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>276</v>
+      </c>
+      <c r="E10" t="n">
+        <v>250.91</v>
+      </c>
+      <c r="F10" t="n">
+        <v>92</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.95</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -4493,30 +3829,20 @@
           <t xml:space="preserve">Fried Beef Patty (150g × 2 pcs)</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.3</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">276</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250.91</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">138</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.95</t>
-        </is>
+      <c r="C11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>276</v>
+      </c>
+      <c r="E11" t="n">
+        <v>250.91</v>
+      </c>
+      <c r="F11" t="n">
+        <v>138</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.95</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -4550,30 +3876,22 @@
           <t xml:space="preserve">Chicken Fillet Ham, Sliced</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.5</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170.91</t>
-        </is>
+      <c r="C12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>188</v>
+      </c>
+      <c r="E12" t="n">
+        <v>170.91</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.01</t>
-        </is>
+      <c r="G12" t="n">
+        <v>2.01</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -4607,30 +3925,22 @@
           <t xml:space="preserve">Cooked-Smoked Chicken Pepperoni (sliced)</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.5</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">274</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249.09</t>
-        </is>
+      <c r="C13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>274</v>
+      </c>
+      <c r="E13" t="n">
+        <v>249.09</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.92</t>
-        </is>
+      <c r="G13" t="n">
+        <v>2.92</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -4664,30 +3974,22 @@
           <t xml:space="preserve">Cooked-Smoked Chicken Pepperoni (whole stick)</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.8</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">457</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">415.45</t>
-        </is>
+      <c r="C14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D14" t="n">
+        <v>457</v>
+      </c>
+      <c r="E14" t="n">
+        <v>415.45</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.88</t>
-        </is>
+      <c r="G14" t="n">
+        <v>4.88</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -4726,25 +4028,19 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">412</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">374.55</t>
-        </is>
+      <c r="D15" t="n">
+        <v>412</v>
+      </c>
+      <c r="E15" t="n">
+        <v>374.55</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.4</t>
-        </is>
+      <c r="G15" t="n">
+        <v>4.4</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -4842,30 +4138,22 @@
           <t xml:space="preserve">Breakfast Sausages (skinless) for Sausage Rolls, 45 g each</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">245</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222.73</t>
-        </is>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>245</v>
+      </c>
+      <c r="E2" t="n">
+        <v>222.73</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.62</t>
-        </is>
+      <c r="G2" t="n">
+        <v>2.62</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -4899,30 +4187,22 @@
           <t xml:space="preserve">Breakfast Sausages</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.4</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">135</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122.73</t>
-        </is>
+      <c r="C3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>135</v>
+      </c>
+      <c r="E3" t="n">
+        <v>122.73</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.44</t>
-        </is>
+      <c r="G3" t="n">
+        <v>1.44</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -4956,30 +4236,22 @@
           <t xml:space="preserve">Tender Sausages</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.4</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164.55</t>
-        </is>
+      <c r="C4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>181</v>
+      </c>
+      <c r="E4" t="n">
+        <v>164.55</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.93</t>
-        </is>
+      <c r="G4" t="n">
+        <v>1.93</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -5013,30 +4285,22 @@
           <t xml:space="preserve">Kazan Milk Sausages</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.4</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">235</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213.64</t>
-        </is>
+      <c r="C5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>235</v>
+      </c>
+      <c r="E5" t="n">
+        <v>213.64</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.51</t>
-        </is>
+      <c r="G5" t="n">
+        <v>2.51</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -5070,30 +4334,22 @@
           <t xml:space="preserve">Cheese Sausages</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.4</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">293</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">266.36</t>
-        </is>
+      <c r="C6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>293</v>
+      </c>
+      <c r="E6" t="n">
+        <v>266.36</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.13</t>
-        </is>
+      <c r="G6" t="n">
+        <v>3.13</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -5127,30 +4383,22 @@
           <t xml:space="preserve">Beef Sausages</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.4</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">284</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258.18</t>
-        </is>
+      <c r="C7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>284</v>
+      </c>
+      <c r="E7" t="n">
+        <v>258.18</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.03</t>
-        </is>
+      <c r="G7" t="n">
+        <v>3.03</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -5184,30 +4432,22 @@
           <t xml:space="preserve">Premium Sausages</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.4</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132.73</t>
-        </is>
+      <c r="C8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>146</v>
+      </c>
+      <c r="E8" t="n">
+        <v>132.73</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.56</t>
-        </is>
+      <c r="G8" t="n">
+        <v>1.56</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -5241,30 +4481,22 @@
           <t xml:space="preserve">Juicy Sausages</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.4</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130.91</t>
-        </is>
+      <c r="C9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>144</v>
+      </c>
+      <c r="E9" t="n">
+        <v>130.91</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.54</t>
-        </is>
+      <c r="G9" t="n">
+        <v>1.54</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -5298,30 +4530,22 @@
           <t xml:space="preserve">Cheese Sausage Links</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.3</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">271</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246.36</t>
-        </is>
+      <c r="C10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>271</v>
+      </c>
+      <c r="E10" t="n">
+        <v>246.36</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.89</t>
-        </is>
+      <c r="G10" t="n">
+        <v>2.89</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -5355,30 +4579,22 @@
           <t xml:space="preserve">Boiled Beef Sausage</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.5</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">265.45</t>
-        </is>
+      <c r="C11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>292</v>
+      </c>
+      <c r="E11" t="n">
+        <v>265.45</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.12</t>
-        </is>
+      <c r="G11" t="n">
+        <v>3.12</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -5412,30 +4628,22 @@
           <t xml:space="preserve">Boiled Assorted Sausage</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.5</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179.09</t>
-        </is>
+      <c r="C12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>197</v>
+      </c>
+      <c r="E12" t="n">
+        <v>179.09</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.1</t>
-        </is>
+      <c r="G12" t="n">
+        <v>2.1</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -5469,30 +4677,22 @@
           <t xml:space="preserve">Boiled Tender Sausage</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.5</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181.82</t>
-        </is>
+      <c r="C13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>200</v>
+      </c>
+      <c r="E13" t="n">
+        <v>181.82</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.14</t>
-        </is>
+      <c r="G13" t="n">
+        <v>2.14</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -5526,30 +4726,22 @@
           <t xml:space="preserve">Turkey Ham</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.5</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">380</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">345.45</t>
-        </is>
+      <c r="C14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>380</v>
+      </c>
+      <c r="E14" t="n">
+        <v>345.45</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.06</t>
-        </is>
+      <c r="G14" t="n">
+        <v>4.06</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -5583,30 +4775,22 @@
           <t xml:space="preserve">Marbled Beef Ham</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.5</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">398</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">361.82</t>
-        </is>
+      <c r="C15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>398</v>
+      </c>
+      <c r="E15" t="n">
+        <v>361.82</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.25</t>
-        </is>
+      <c r="G15" t="n">
+        <v>4.25</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -5640,30 +4824,22 @@
           <t xml:space="preserve">Chicken Ham</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.5</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">350</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">318.18</t>
-        </is>
+      <c r="C16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>350</v>
+      </c>
+      <c r="E16" t="n">
+        <v>318.18</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.74</t>
-        </is>
+      <c r="G16" t="n">
+        <v>3.74</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -5697,30 +4873,22 @@
           <t xml:space="preserve">Khan Cervelat</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.45</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196.36</t>
-        </is>
+      <c r="C17" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D17" t="n">
+        <v>216</v>
+      </c>
+      <c r="E17" t="n">
+        <v>196.36</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.31</t>
-        </is>
+      <c r="G17" t="n">
+        <v>2.31</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -5754,30 +4922,22 @@
           <t xml:space="preserve">Tatar-Style Smoked Cervelat</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.45</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">298</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">270.91</t>
-        </is>
+      <c r="C18" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D18" t="n">
+        <v>298</v>
+      </c>
+      <c r="E18" t="n">
+        <v>270.91</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.18</t>
-        </is>
+      <c r="G18" t="n">
+        <v>3.18</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -5811,30 +4971,22 @@
           <t xml:space="preserve">Semi-Smoked Turkey Sausage</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.45</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">348</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">316.36</t>
-        </is>
+      <c r="C19" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D19" t="n">
+        <v>348</v>
+      </c>
+      <c r="E19" t="n">
+        <v>316.36</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.71</t>
-        </is>
+      <c r="G19" t="n">
+        <v>3.71</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -5868,30 +5020,22 @@
           <t xml:space="preserve">Semi-Smoked Beef Sausage</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.45</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">358</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">325.45</t>
-        </is>
+      <c r="C20" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D20" t="n">
+        <v>358</v>
+      </c>
+      <c r="E20" t="n">
+        <v>325.45</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.82</t>
-        </is>
+      <c r="G20" t="n">
+        <v>3.82</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -5925,30 +5069,22 @@
           <t xml:space="preserve">Ramazan Smoked Sausage</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.54</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">377</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">342.73</t>
-        </is>
+      <c r="C21" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="D21" t="n">
+        <v>377</v>
+      </c>
+      <c r="E21" t="n">
+        <v>342.73</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.02</t>
-        </is>
+      <c r="G21" t="n">
+        <v>4.02</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -5982,30 +5118,22 @@
           <t xml:space="preserve">Ramazan Smoked Sausage (half)</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.27</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170.91</t>
-        </is>
+      <c r="C22" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="D22" t="n">
+        <v>188</v>
+      </c>
+      <c r="E22" t="n">
+        <v>170.91</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.01</t>
-        </is>
+      <c r="G22" t="n">
+        <v>2.01</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -6039,30 +5167,22 @@
           <t xml:space="preserve">Marbled Smoked Sausage</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.54</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">362</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">329.09</t>
-        </is>
+      <c r="C23" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="D23" t="n">
+        <v>362</v>
+      </c>
+      <c r="E23" t="n">
+        <v>329.09</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.86</t>
-        </is>
+      <c r="G23" t="n">
+        <v>3.86</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -6096,30 +5216,22 @@
           <t xml:space="preserve">Marbled Smoked Sausage (half)</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.27</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164.55</t>
-        </is>
+      <c r="C24" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="D24" t="n">
+        <v>181</v>
+      </c>
+      <c r="E24" t="n">
+        <v>164.55</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.93</t>
-        </is>
+      <c r="G24" t="n">
+        <v>1.93</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -6153,30 +5265,22 @@
           <t xml:space="preserve">Fillet Smoked Sausage</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.54</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">333</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">302.73</t>
-        </is>
+      <c r="C25" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="D25" t="n">
+        <v>333</v>
+      </c>
+      <c r="E25" t="n">
+        <v>302.73</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.55</t>
-        </is>
+      <c r="G25" t="n">
+        <v>3.55</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -6210,30 +5314,22 @@
           <t xml:space="preserve">Fillet Smoked Sausage (half)</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.27</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150.91</t>
-        </is>
+      <c r="C26" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="D26" t="n">
+        <v>166</v>
+      </c>
+      <c r="E26" t="n">
+        <v>150.91</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.77</t>
-        </is>
+      <c r="G26" t="n">
+        <v>1.77</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -6267,30 +5363,22 @@
           <t xml:space="preserve">Knyazheskaya Smoked Sausage</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.54</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">362</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">329.09</t>
-        </is>
+      <c r="C27" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="D27" t="n">
+        <v>362</v>
+      </c>
+      <c r="E27" t="n">
+        <v>329.09</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.86</t>
-        </is>
+      <c r="G27" t="n">
+        <v>3.86</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -6324,30 +5412,22 @@
           <t xml:space="preserve">Knyazheskaya Smoked Sausage (half)</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.27</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164.55</t>
-        </is>
+      <c r="C28" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="D28" t="n">
+        <v>181</v>
+      </c>
+      <c r="E28" t="n">
+        <v>164.55</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.93</t>
-        </is>
+      <c r="G28" t="n">
+        <v>1.93</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -6381,30 +5461,22 @@
           <t xml:space="preserve">Kazylyk Premium (gift box, horse meat)</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.2</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">650</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">541.67</t>
-        </is>
+      <c r="C29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D29" t="n">
+        <v>650</v>
+      </c>
+      <c r="E29" t="n">
+        <v>541.67</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6.36</t>
-        </is>
+      <c r="G29" t="n">
+        <v>6.36</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -6438,30 +5510,22 @@
           <t xml:space="preserve">Kazylyk Premium Sliced (gift box, horse meat)</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.1</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">450</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">375</t>
-        </is>
+      <c r="C30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>450</v>
+      </c>
+      <c r="E30" t="n">
+        <v>375</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.4</t>
-        </is>
+      <c r="G30" t="n">
+        <v>4.4</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -6559,30 +5623,20 @@
           <t xml:space="preserve">Gubadiya with Kort (Tatar layered pie)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">59.93</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">54.48</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">59.93</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.64</t>
-        </is>
+      <c r="C2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>59.93</v>
+      </c>
+      <c r="E2" t="n">
+        <v>54.48</v>
+      </c>
+      <c r="F2" t="n">
+        <v>59.93</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.64</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -6616,30 +5670,20 @@
           <t xml:space="preserve">Fried Cheburek</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">61.81</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">56.19</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">61.81</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.66</t>
-        </is>
+      <c r="C3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>61.81</v>
+      </c>
+      <c r="E3" t="n">
+        <v>56.19</v>
+      </c>
+      <c r="F3" t="n">
+        <v>61.81</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.66</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -6673,30 +5717,20 @@
           <t xml:space="preserve">Fried Peremyach (Tatar meat pie)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">63.29</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57.54</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">63.29</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.68</t>
-        </is>
+      <c r="C4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>63.29</v>
+      </c>
+      <c r="E4" t="n">
+        <v>57.54</v>
+      </c>
+      <c r="F4" t="n">
+        <v>63.29</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.68</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -6730,30 +5764,20 @@
           <t xml:space="preserve">Chicken Samsa</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.12</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66.05</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60.05</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66.05</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.71</t>
-        </is>
+      <c r="C5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D5" t="n">
+        <v>66.05</v>
+      </c>
+      <c r="E5" t="n">
+        <v>60.05</v>
+      </c>
+      <c r="F5" t="n">
+        <v>66.05</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.71</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -6787,30 +5811,20 @@
           <t xml:space="preserve">Echpochmak with Beef &amp; Potato (Tatar triangle pie)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">73.58</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66.89</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">73.58</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.79</t>
-        </is>
+      <c r="C6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>73.58</v>
+      </c>
+      <c r="E6" t="n">
+        <v>66.89</v>
+      </c>
+      <c r="F6" t="n">
+        <v>73.58</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.79</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -6844,30 +5858,20 @@
           <t xml:space="preserve">Beef Samsa</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.12</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">78.28</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71.16</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">78.28</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.84</t>
-        </is>
+      <c r="C7" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D7" t="n">
+        <v>78.28</v>
+      </c>
+      <c r="E7" t="n">
+        <v>71.16</v>
+      </c>
+      <c r="F7" t="n">
+        <v>78.28</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.84</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -6901,30 +5905,20 @@
           <t xml:space="preserve">Elesh with Chicken &amp; Potato (Tatar pie)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.15</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">83.29</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">75.72</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">83.29</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.89</t>
-        </is>
+      <c r="C8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D8" t="n">
+        <v>83.29</v>
+      </c>
+      <c r="E8" t="n">
+        <v>75.72</v>
+      </c>
+      <c r="F8" t="n">
+        <v>83.29</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.89</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -6958,30 +5952,20 @@
           <t xml:space="preserve">Беккен с капустой</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52.97</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48.15</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52.97</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.57</t>
-        </is>
+      <c r="C9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>52.97</v>
+      </c>
+      <c r="E9" t="n">
+        <v>48.15</v>
+      </c>
+      <c r="F9" t="n">
+        <v>52.97</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.57</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -7015,30 +5999,20 @@
           <t xml:space="preserve">Вак балиш</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.1</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66.32</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60.29</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66.32</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.71</t>
-        </is>
+      <c r="C10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>66.32</v>
+      </c>
+      <c r="E10" t="n">
+        <v>60.29</v>
+      </c>
+      <c r="F10" t="n">
+        <v>66.32</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.71</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -7072,25 +6046,19 @@
           <t xml:space="preserve">Chak-Chak (plastic pack)</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.3</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211.8</t>
-        </is>
+      <c r="C11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>211.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211.8</t>
-        </is>
+      <c r="F11" t="n">
+        <v>211.8</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -7129,25 +6097,19 @@
           <t xml:space="preserve">Chak-Chak (craft gift box)</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.3</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">295.57</t>
-        </is>
+      <c r="C12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>295.57</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">295.57</t>
-        </is>
+      <c r="F12" t="n">
+        <v>295.57</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -7186,30 +6148,20 @@
           <t xml:space="preserve">Cottage Cheese Sochnik</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.1</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">47.08</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42.8</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">47.08</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.5</t>
-        </is>
+      <c r="C13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>47.08</v>
+      </c>
+      <c r="E13" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="F13" t="n">
+        <v>47.08</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.5</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -7243,30 +6195,20 @@
           <t xml:space="preserve">Пирожок жареный с картофелем</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.1</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50.92</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46.29</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50.92</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.54</t>
-        </is>
+      <c r="C14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>50.92</v>
+      </c>
+      <c r="E14" t="n">
+        <v>46.29</v>
+      </c>
+      <c r="F14" t="n">
+        <v>50.92</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.54</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -7300,30 +6242,20 @@
           <t xml:space="preserve">Syrnik (cottage cheese pancake)</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.07</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48.26</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">43.87</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48.26</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.52</t>
-        </is>
+      <c r="C15" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="D15" t="n">
+        <v>48.26</v>
+      </c>
+      <c r="E15" t="n">
+        <v>43.87</v>
+      </c>
+      <c r="F15" t="n">
+        <v>48.26</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.52</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -7357,30 +6289,20 @@
           <t xml:space="preserve">Apple Pie</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.1</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52.97</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48.15</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52.97</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.57</t>
-        </is>
+      <c r="C16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>52.97</v>
+      </c>
+      <c r="E16" t="n">
+        <v>48.15</v>
+      </c>
+      <c r="F16" t="n">
+        <v>52.97</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.57</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -7414,30 +6336,20 @@
           <t xml:space="preserve">Spring Onion &amp; Egg Pie</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.1</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">67.73</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">61.57</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">67.73</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.72</t>
-        </is>
+      <c r="C17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>67.73</v>
+      </c>
+      <c r="E17" t="n">
+        <v>61.57</v>
+      </c>
+      <c r="F17" t="n">
+        <v>67.73</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.72</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -7471,30 +6383,20 @@
           <t xml:space="preserve">Orange Muffin</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.1</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72.26</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">65.69</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72.26</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.77</t>
-        </is>
+      <c r="C18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>72.26</v>
+      </c>
+      <c r="E18" t="n">
+        <v>65.69</v>
+      </c>
+      <c r="F18" t="n">
+        <v>72.26</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.77</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -7528,30 +6430,20 @@
           <t xml:space="preserve">Sausage Roll</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.12</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72.49</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">65.9</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72.49</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.77</t>
-        </is>
+      <c r="C19" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D19" t="n">
+        <v>72.49</v>
+      </c>
+      <c r="E19" t="n">
+        <v>65.9</v>
+      </c>
+      <c r="F19" t="n">
+        <v>72.49</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.77</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -7585,30 +6477,20 @@
           <t xml:space="preserve">Cherry Pie</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.1</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">75.08</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68.25</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">75.08</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.8</t>
-        </is>
+      <c r="C20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>75.08</v>
+      </c>
+      <c r="E20" t="n">
+        <v>68.25</v>
+      </c>
+      <c r="F20" t="n">
+        <v>75.08</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.8</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -7642,30 +6524,20 @@
           <t xml:space="preserve">Chocolate &amp; Nut Croissant</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.09</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">77.51</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70.46</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">77.51</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.83</t>
-        </is>
+      <c r="C21" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="D21" t="n">
+        <v>77.51</v>
+      </c>
+      <c r="E21" t="n">
+        <v>70.46</v>
+      </c>
+      <c r="F21" t="n">
+        <v>77.51</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.83</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -7699,30 +6571,20 @@
           <t xml:space="preserve">Chocolate Muffin</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.1</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">78.78</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71.62</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">78.78</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.84</t>
-        </is>
+      <c r="C22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>78.78</v>
+      </c>
+      <c r="E22" t="n">
+        <v>71.62</v>
+      </c>
+      <c r="F22" t="n">
+        <v>78.78</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.84</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -7756,30 +6618,20 @@
           <t xml:space="preserve">Слойка с ветчиной и сыром</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.09</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108.15</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98.32</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108.15</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.15</t>
-        </is>
+      <c r="C23" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="D23" t="n">
+        <v>108.15</v>
+      </c>
+      <c r="E23" t="n">
+        <v>98.32</v>
+      </c>
+      <c r="F23" t="n">
+        <v>108.15</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.15</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
